--- a/MOSData_clean_mirror.xlsx
+++ b/MOSData_clean_mirror.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1359,16 +1359,1089 @@
         <v>-7710998.41</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>Dt/Time:28/06/2026 4:44:25 PM</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>MERCANTILE OFFICE SYSTEMS PVT. LTD. 82-83</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>Trial Balance - Normal Date To Date</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>Report Date From 01/04/2082 To 13/03/2083</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>Account Group / Ledger</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B39" t="str">
+        <v>6010</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ADMINISTRATIVE EXPENSES</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Operating Expense</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>22167664.62</v>
+      </c>
+      <c r="H39">
+        <v>182167.61</v>
+      </c>
+      <c r="I39">
+        <v>21985497.01</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B40" t="str">
+        <v>1030</v>
+      </c>
+      <c r="C40" t="str">
+        <v>BALANCE IN BANK</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F40">
+        <v>-23227538.79</v>
+      </c>
+      <c r="G40">
+        <v>2746645107.61</v>
+      </c>
+      <c r="H40">
+        <v>2760165377.15</v>
+      </c>
+      <c r="I40">
+        <v>-36747808.33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B41" t="str">
+        <v>1040</v>
+      </c>
+      <c r="C41" t="str">
+        <v>BANK GUARANTEE</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F41">
+        <v>591047.52</v>
+      </c>
+      <c r="G41">
+        <v>1407967.5</v>
+      </c>
+      <c r="H41">
+        <v>1690731.25</v>
+      </c>
+      <c r="I41">
+        <v>308283.77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B42" t="str">
+        <v>1010</v>
+      </c>
+      <c r="C42" t="str">
+        <v>CASH &amp; BANK</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F42">
+        <v>-71021.6</v>
+      </c>
+      <c r="G42">
+        <v>20453132.9</v>
+      </c>
+      <c r="H42">
+        <v>19845631.81</v>
+      </c>
+      <c r="I42">
+        <v>536479.49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B43" t="str">
+        <v>1020</v>
+      </c>
+      <c r="C43" t="str">
+        <v>CASH IN HAND</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F43">
+        <v>625516.03</v>
+      </c>
+      <c r="G43">
+        <v>8184106</v>
+      </c>
+      <c r="H43">
+        <v>8310994.98</v>
+      </c>
+      <c r="I43">
+        <v>498627.05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B44" t="str">
+        <v>5000</v>
+      </c>
+      <c r="C44" t="str">
+        <v>COST OF GOODS SOLD</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E44" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>330407532.37</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>330407532.37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2110</v>
+      </c>
+      <c r="C45" t="str">
+        <v>DEMAND LOAN</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F45">
+        <v>-211159656.83</v>
+      </c>
+      <c r="G45">
+        <v>410785221.09</v>
+      </c>
+      <c r="H45">
+        <v>257285493.12</v>
+      </c>
+      <c r="I45">
+        <v>-57659928.86</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B46" t="str">
+        <v>1130</v>
+      </c>
+      <c r="C46" t="str">
+        <v>DEPOSIT</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F46">
+        <v>5700506.65</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>5700506.65</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2530</v>
+      </c>
+      <c r="C47" t="str">
+        <v>DIRECTORS LOAN</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Long Term Liability</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>88646691.42</v>
+      </c>
+      <c r="H47">
+        <v>119252458.33</v>
+      </c>
+      <c r="I47">
+        <v>-30605766.91</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B48" t="str">
+        <v>6050</v>
+      </c>
+      <c r="C48" t="str">
+        <v>EXPENDITURE</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Operating Expense</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>235719651.89</v>
+      </c>
+      <c r="H48">
+        <v>1151.62</v>
+      </c>
+      <c r="I48">
+        <v>235718500.27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2520</v>
+      </c>
+      <c r="C49" t="str">
+        <v>HIRE PURCHASE LOAN</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Long Term Liability</v>
+      </c>
+      <c r="F49">
+        <v>-3321214.26</v>
+      </c>
+      <c r="G49">
+        <v>484687.71</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>-2836526.55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B50" t="str">
+        <v>4100</v>
+      </c>
+      <c r="C50" t="str">
+        <v>INCOME</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Revenue</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Operating Income</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>45.14</v>
+      </c>
+      <c r="H50">
+        <v>233653177.85</v>
+      </c>
+      <c r="I50">
+        <v>-233653132.71</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B51" t="str">
+        <v>1200</v>
+      </c>
+      <c r="C51" t="str">
+        <v>INTER COMPANY BALANCE</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F51">
+        <v>109304320.33</v>
+      </c>
+      <c r="G51">
+        <v>51850282</v>
+      </c>
+      <c r="H51">
+        <v>195800000</v>
+      </c>
+      <c r="I51">
+        <v>-34645397.67</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B52" t="str">
+        <v>6100</v>
+      </c>
+      <c r="C52" t="str">
+        <v>LESS FINANCING COST</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Finance Cost</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>30049410.79</v>
+      </c>
+      <c r="H52">
+        <v>4167.93</v>
+      </c>
+      <c r="I52">
+        <v>30045242.86</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B53" t="str">
+        <v>1050</v>
+      </c>
+      <c r="C53" t="str">
+        <v>LETTER OF CREDIT</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F53">
+        <v>10329141.06</v>
+      </c>
+      <c r="G53">
+        <v>371097786.31</v>
+      </c>
+      <c r="H53">
+        <v>38096439.43</v>
+      </c>
+      <c r="I53">
+        <v>343330487.94</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2040</v>
+      </c>
+      <c r="C54" t="str">
+        <v>LIABILITIES</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F54">
+        <v>-10000000</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>-10000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B55" t="str">
+        <v>1120</v>
+      </c>
+      <c r="C55" t="str">
+        <v>LOANS &amp; ADVANCE</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F55">
+        <v>13593517.28</v>
+      </c>
+      <c r="G55">
+        <v>260400.95</v>
+      </c>
+      <c r="H55">
+        <v>750</v>
+      </c>
+      <c r="I55">
+        <v>13853168.23</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2020</v>
+      </c>
+      <c r="C56" t="str">
+        <v>OTHER PAYABLES</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F56">
+        <v>-1391813.55</v>
+      </c>
+      <c r="G56">
+        <v>18117149.62</v>
+      </c>
+      <c r="H56">
+        <v>19539373.14</v>
+      </c>
+      <c r="I56">
+        <v>-2814037.07</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B57" t="str">
+        <v>1110</v>
+      </c>
+      <c r="C57" t="str">
+        <v>OTHER RECEIVABLES</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F57">
+        <v>11245674.15</v>
+      </c>
+      <c r="G57">
+        <v>78440343.69</v>
+      </c>
+      <c r="H57">
+        <v>2344072.07</v>
+      </c>
+      <c r="I57">
+        <v>87341945.77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B58" t="str">
+        <v>6020</v>
+      </c>
+      <c r="C58" t="str">
+        <v>PAYROLL RELATED EXPENSES</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Operating Expense</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>25621404.31</v>
+      </c>
+      <c r="H58">
+        <v>247707.58</v>
+      </c>
+      <c r="I58">
+        <v>25373696.73</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B59" t="str">
+        <v>1500</v>
+      </c>
+      <c r="C59" t="str">
+        <v>PROPERTY, PLANT &amp; EQUIPMENT</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Fixed Asset</v>
+      </c>
+      <c r="F59">
+        <v>12051184.09</v>
+      </c>
+      <c r="G59">
+        <v>361608.43</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>12412792.52</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B60" t="str">
+        <v>1510</v>
+      </c>
+      <c r="C60" t="str">
+        <v>PROPERTY, PLANT &amp; EQUIPMENTS</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Fixed Asset</v>
+      </c>
+      <c r="F60">
+        <v>3205207.51</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>3205207.51</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B61" t="str">
+        <v>3100</v>
+      </c>
+      <c r="C61" t="str">
+        <v>RESERVE &amp; SERPLUS</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Equity</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Equity</v>
+      </c>
+      <c r="F61">
+        <v>-193802238.23</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>-193802238.23</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B62" t="str">
+        <v>4000</v>
+      </c>
+      <c r="C62" t="str">
+        <v>REVENUE</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Revenue</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Operating Income</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>40390601.92</v>
+      </c>
+      <c r="H62">
+        <v>382213513.36</v>
+      </c>
+      <c r="I62">
+        <v>-341822911.44</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B63" t="str">
+        <v>6030</v>
+      </c>
+      <c r="C63" t="str">
+        <v>SALES &amp; MARKETING EXPENSES</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Operating Expense</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>4970079.32</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>4970079.32</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2120</v>
+      </c>
+      <c r="C64" t="str">
+        <v>SHORT TERM LOAN</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F64">
+        <v>-180496000</v>
+      </c>
+      <c r="G64">
+        <v>278865908.31</v>
+      </c>
+      <c r="H64">
+        <v>298150000</v>
+      </c>
+      <c r="I64">
+        <v>-199780091.69</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2030</v>
+      </c>
+      <c r="C65" t="str">
+        <v>STATUTORY LIABILITES</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F65">
+        <v>-4636885.92</v>
+      </c>
+      <c r="G65">
+        <v>17489179.56</v>
+      </c>
+      <c r="H65">
+        <v>83564608.54</v>
+      </c>
+      <c r="I65">
+        <v>-70712314.9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2010</v>
+      </c>
+      <c r="C66" t="str">
+        <v>SUNDRY CREDITORS</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F66">
+        <v>21521331.53</v>
+      </c>
+      <c r="G66">
+        <v>269873368.31</v>
+      </c>
+      <c r="H66">
+        <v>698484036.33</v>
+      </c>
+      <c r="I66">
+        <v>-407089336.49</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B67" t="str">
+        <v>1100</v>
+      </c>
+      <c r="C67" t="str">
+        <v>SUNDRY DEBTORS</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Assets</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Current Asset</v>
+      </c>
+      <c r="F67">
+        <v>106617499.37</v>
+      </c>
+      <c r="G67">
+        <v>675084065.31</v>
+      </c>
+      <c r="H67">
+        <v>607346601.87</v>
+      </c>
+      <c r="I67">
+        <v>174354962.81</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2510</v>
+      </c>
+      <c r="C68" t="str">
+        <v>TERM LOAN</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Long Term Liability</v>
+      </c>
+      <c r="F68">
+        <v>-42878429.18</v>
+      </c>
+      <c r="G68">
+        <v>276849489.65</v>
+      </c>
+      <c r="H68">
+        <v>275652454.62</v>
+      </c>
+      <c r="I68">
+        <v>-41681394.15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B69" t="str">
+        <v>6040</v>
+      </c>
+      <c r="C69" t="str">
+        <v>TRAVELLING EXPENSES</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Operating Expense</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>633265.19</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>633265.19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2130</v>
+      </c>
+      <c r="C70" t="str">
+        <v>USANCE LOAN</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Liabilities</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Current Liability</v>
+      </c>
+      <c r="F70">
+        <v>-4685755.08</v>
+      </c>
+      <c r="G70">
+        <v>133154629.59</v>
+      </c>
+      <c r="H70">
+        <v>136179872.92</v>
+      </c>
+      <c r="I70">
+        <v>-7710998.41</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2182,16 +3255,828 @@
         <v>33000</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>BIJAY KUMAR SHRESTHA</v>
+      </c>
+      <c r="C29">
+        <v>107</v>
+      </c>
+      <c r="D29">
+        <v>7365241.95</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>45073960.57</v>
+      </c>
+      <c r="G29">
+        <v>4393115.87</v>
+      </c>
+      <c r="H29">
+        <v>4191585.27</v>
+      </c>
+      <c r="I29">
+        <v>53658661.71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Dinesh KC</v>
+      </c>
+      <c r="C30">
+        <v>33</v>
+      </c>
+      <c r="D30">
+        <v>1723500</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>28199533.87</v>
+      </c>
+      <c r="G30">
+        <v>2007518.27</v>
+      </c>
+      <c r="H30">
+        <v>86213.61</v>
+      </c>
+      <c r="I30">
+        <v>30293265.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B31" t="str">
+        <v>BABITA TIMALSINA</v>
+      </c>
+      <c r="C31">
+        <v>35</v>
+      </c>
+      <c r="D31">
+        <v>1759765</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>25552610.43</v>
+      </c>
+      <c r="G31">
+        <v>1479528</v>
+      </c>
+      <c r="H31">
+        <v>34148.85</v>
+      </c>
+      <c r="I31">
+        <v>27066287.28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B32" t="str">
+        <v>PRAKASH GYAWALI</v>
+      </c>
+      <c r="C32">
+        <v>46</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>10485.3</v>
+      </c>
+      <c r="G32">
+        <v>1000</v>
+      </c>
+      <c r="H32">
+        <v>11237210.33</v>
+      </c>
+      <c r="I32">
+        <v>11248695.63</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B33" t="str">
+        <v>SURAJ B. CHHETRI</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>9314498.93</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>9314498.93</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B34" t="str">
+        <v>SHOWROOM</v>
+      </c>
+      <c r="C34">
+        <v>87</v>
+      </c>
+      <c r="D34">
+        <v>407591</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>740761.61</v>
+      </c>
+      <c r="G34">
+        <v>2861272.09</v>
+      </c>
+      <c r="H34">
+        <v>4377798.06</v>
+      </c>
+      <c r="I34">
+        <v>7979831.76</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B35" t="str">
+        <v>UTSAV SHUMSHER THAPA</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <v>586000</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>3717800</v>
+      </c>
+      <c r="G35">
+        <v>1460.18</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>3719260.18</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B36" t="str">
+        <v>SURAJ BASNET</v>
+      </c>
+      <c r="C36">
+        <v>16</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>3687324.72</v>
+      </c>
+      <c r="I36">
+        <v>3687324.72</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B37" t="str">
+        <v>KARNA PRASAD PARAJULI</v>
+      </c>
+      <c r="C37">
+        <v>33</v>
+      </c>
+      <c r="D37">
+        <v>1397502.46</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>62500</v>
+      </c>
+      <c r="G37">
+        <v>96999.97</v>
+      </c>
+      <c r="H37">
+        <v>2344087.81</v>
+      </c>
+      <c r="I37">
+        <v>2503587.78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B38" t="str">
+        <v>BHIMSEN BASNET</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>154200</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>2455200</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>2455200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B39" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="C39">
+        <v>47</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>2073515.76</v>
+      </c>
+      <c r="I39">
+        <v>2073515.76</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B40" t="str">
+        <v>OLD-RAJ</v>
+      </c>
+      <c r="C40">
+        <v>24</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1402194.52</v>
+      </c>
+      <c r="I40">
+        <v>1402194.52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B41" t="str">
+        <v>BIKRAM RAJBHANDARI</v>
+      </c>
+      <c r="C41">
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>753069.79</v>
+      </c>
+      <c r="I41">
+        <v>753069.79</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B42" t="str">
+        <v>OLD-KABIN</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>491883</v>
+      </c>
+      <c r="I42">
+        <v>491883</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B43" t="str">
+        <v>OFFICE</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>4220</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>376200</v>
+      </c>
+      <c r="I43">
+        <v>380420</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B44" t="str">
+        <v>MARKETING</v>
+      </c>
+      <c r="C44">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>35000</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>133580</v>
+      </c>
+      <c r="G44">
+        <v>9530</v>
+      </c>
+      <c r="H44">
+        <v>184576.15</v>
+      </c>
+      <c r="I44">
+        <v>327686.15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B45" t="str">
+        <v>CHET NATH GURAGAIN</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>288462.18</v>
+      </c>
+      <c r="I45">
+        <v>288462.18</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B46" t="str">
+        <v>SHANKAR RAJ GURAGAIN</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>212400</v>
+      </c>
+      <c r="G46">
+        <v>290</v>
+      </c>
+      <c r="H46">
+        <v>26321.47</v>
+      </c>
+      <c r="I46">
+        <v>239011.47</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B47" t="str">
+        <v>OLD-HIMAL</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>179500</v>
+      </c>
+      <c r="I47">
+        <v>179500</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B48" t="str">
+        <v>BIBEK HADA</v>
+      </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>158829.98</v>
+      </c>
+      <c r="I48">
+        <v>158829.98</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B49" t="str">
+        <v>OLD-JITEN</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>89863.73</v>
+      </c>
+      <c r="I49">
+        <v>89863.73</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B50" t="str">
+        <v>SUBASH KUNWAR</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>81769.97</v>
+      </c>
+      <c r="I50">
+        <v>81769.97</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B51" t="str">
+        <v>SABINA PRADHAN</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>11300</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>17601.8</v>
+      </c>
+      <c r="H51">
+        <v>54000</v>
+      </c>
+      <c r="I51">
+        <v>71601.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Suzita</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>32960</v>
+      </c>
+      <c r="G52">
+        <v>8799.9</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>41759.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B53" t="str">
+        <v>OLD-SUNNY</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>41512.95</v>
+      </c>
+      <c r="I53">
+        <v>41512.95</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B54" t="str">
+        <v>SATISH THANI</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>33000</v>
+      </c>
+      <c r="I54">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B55" t="str">
+        <v>(Unassigned)</v>
+      </c>
+      <c r="C55">
+        <v>7</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>-900</v>
+      </c>
+      <c r="F56">
+        <v>180</v>
+      </c>
+      <c r="G56">
+        <v>720</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2479,16 +4364,276 @@
         <v>75000.87</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Other</v>
+      </c>
+      <c r="C12">
+        <v>589</v>
+      </c>
+      <c r="D12">
+        <v>177137.68</v>
+      </c>
+      <c r="E12">
+        <v>609719.46</v>
+      </c>
+      <c r="F12">
+        <v>23666.92</v>
+      </c>
+      <c r="G12">
+        <v>131864116.93</v>
+      </c>
+      <c r="H12">
+        <v>132674640.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Printers &amp; Consumables</v>
+      </c>
+      <c r="C13">
+        <v>697</v>
+      </c>
+      <c r="D13">
+        <v>4848338.74</v>
+      </c>
+      <c r="E13">
+        <v>25410776.89</v>
+      </c>
+      <c r="F13">
+        <v>22951215.85</v>
+      </c>
+      <c r="G13">
+        <v>69238989.32</v>
+      </c>
+      <c r="H13">
+        <v>122449320.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Systems &amp; Devices</v>
+      </c>
+      <c r="C14">
+        <v>372</v>
+      </c>
+      <c r="D14">
+        <v>17863794.53</v>
+      </c>
+      <c r="E14">
+        <v>1391683.05</v>
+      </c>
+      <c r="F14">
+        <v>317013.72</v>
+      </c>
+      <c r="G14">
+        <v>31210567.47</v>
+      </c>
+      <c r="H14">
+        <v>50783058.77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Monitors &amp; Displays</v>
+      </c>
+      <c r="C15">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>58431.26</v>
+      </c>
+      <c r="E15">
+        <v>4070597.56</v>
+      </c>
+      <c r="F15">
+        <v>140759.62</v>
+      </c>
+      <c r="G15">
+        <v>2110562.22</v>
+      </c>
+      <c r="H15">
+        <v>6380350.66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Networking</v>
+      </c>
+      <c r="C16">
+        <v>82</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>5204860.27</v>
+      </c>
+      <c r="H16">
+        <v>5204860.27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Components &amp; Parts</v>
+      </c>
+      <c r="C17">
+        <v>207</v>
+      </c>
+      <c r="D17">
+        <v>31198.19</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>5134813.56</v>
+      </c>
+      <c r="H17">
+        <v>5166011.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Peripherals</v>
+      </c>
+      <c r="C18">
+        <v>65</v>
+      </c>
+      <c r="D18">
+        <v>30324.82</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>4912662.02</v>
+      </c>
+      <c r="H18">
+        <v>4942986.84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Cables &amp; Adaptors</v>
+      </c>
+      <c r="C19">
+        <v>79</v>
+      </c>
+      <c r="D19">
+        <v>51069.71</v>
+      </c>
+      <c r="E19">
+        <v>8783.39</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>2404326.48</v>
+      </c>
+      <c r="H19">
+        <v>2464179.58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Storage</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>290441.5</v>
+      </c>
+      <c r="H20">
+        <v>290441.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Memory (RAM)</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>75000.87</v>
+      </c>
+      <c r="H21">
+        <v>75000.87</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2616,9 +4761,331 @@
         <v>8000000</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B10" t="str">
+        <v>NOTE BOOK</v>
+      </c>
+      <c r="C10">
+        <v>238108772.57</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B11" t="str">
+        <v>EPSON PRINTER</v>
+      </c>
+      <c r="C11">
+        <v>109168230.61</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B12" t="str">
+        <v>EPSON PROJECTOR</v>
+      </c>
+      <c r="C12">
+        <v>76785025.2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B13" t="str">
+        <v>DESKTOP</v>
+      </c>
+      <c r="C13">
+        <v>48776637.24</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ACER PROJECTOR</v>
+      </c>
+      <c r="C14">
+        <v>18745206</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B15" t="str">
+        <v>EPSON CONSUMABLES</v>
+      </c>
+      <c r="C15">
+        <v>17266696.44</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B16" t="str">
+        <v>MONITOR</v>
+      </c>
+      <c r="C16">
+        <v>6664778.87</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B17" t="str">
+        <v>EPSON SPARES</v>
+      </c>
+      <c r="C17">
+        <v>6000140.53</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B18" t="str">
+        <v>EPSON SCANNER</v>
+      </c>
+      <c r="C18">
+        <v>4889814.32</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B19" t="str">
+        <v>No Sub Group</v>
+      </c>
+      <c r="C19">
+        <v>1083655.2</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SINGLE FUNCTION</v>
+      </c>
+      <c r="C20">
+        <v>653694.71</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SPARE</v>
+      </c>
+      <c r="C21">
+        <v>82194.68</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SCREEN</v>
+      </c>
+      <c r="C22">
+        <v>76106.19</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B23" t="str">
+        <v>POWER SUPPLY</v>
+      </c>
+      <c r="C23">
+        <v>49999.98</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B24" t="str">
+        <v>ACESSORIES</v>
+      </c>
+      <c r="C24">
+        <v>4159.29</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Epson Printers</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>250000000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Acer Laptops</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>300000000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Acer Desktops</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>225000000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Monitors &amp; Displays</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Epson Conusmables</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Components &amp; Parts</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Cables &amp; Adaptors</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Other</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>3000000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
   </ignoredErrors>
 </worksheet>
 </file>